--- a/data/trans_orig/P04C04_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>405560</t>
+          <t>405588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>439493</t>
+          <t>439357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>358743</t>
+          <t>357479</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>383824</t>
+          <t>383340</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>775100</t>
+          <t>771655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>815635</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>12279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56023</t>
+          <t>56947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89905</t>
+          <t>88326</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54021</t>
+          <t>55163</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79072</t>
+          <t>79434</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119680</t>
+          <t>119780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>157637</t>
+          <t>161569</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370602</t>
+          <t>370326</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400917</t>
+          <t>400275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306268</t>
+          <t>305926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328205</t>
+          <t>329010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>685547</t>
+          <t>684593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723931</t>
+          <t>721639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>571</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48514</t>
+          <t>47702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78299</t>
+          <t>78117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49560</t>
+          <t>49051</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71807</t>
+          <t>71647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102909</t>
+          <t>105410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141414</t>
+          <t>141473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135573</t>
+          <t>151959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>582446</t>
+          <t>581549</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138152</t>
+          <t>138303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150923</t>
+          <t>151034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>217373</t>
+          <t>195890</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>727173</t>
+          <t>728296</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75767</t>
+          <t>77591</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>528127</t>
+          <t>511679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>27691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96131</t>
+          <t>96383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>611031</t>
+          <t>636965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>847654</t>
+          <t>844663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>903140</t>
+          <t>904589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>845596</t>
+          <t>844306</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>929436</t>
+          <t>927210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1715376</t>
+          <t>1711303</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1830352</t>
+          <t>1828483</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28321</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118429</t>
+          <t>118328</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>176159</t>
+          <t>177768</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45240</t>
+          <t>46329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>124942</t>
+          <t>125056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>167408</t>
+          <t>169227</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>277441</t>
+          <t>280074</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>401126</t>
+          <t>400159</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>429899</t>
+          <t>431383</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>461879</t>
+          <t>494173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>730835</t>
+          <t>731263</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>873183</t>
+          <t>894738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1149620</t>
+          <t>1149629</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>25882</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36012</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62353</t>
+          <t>63041</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99697</t>
+          <t>99318</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>373196</t>
+          <t>339751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>146274</t>
+          <t>146464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434999</t>
+          <t>405137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156420</t>
+          <t>158122</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>205812</t>
+          <t>208805</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>641433</t>
+          <t>641247</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>675144</t>
+          <t>675070</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>808146</t>
+          <t>807836</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>872738</t>
+          <t>871519</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20741</t>
+          <t>20685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28990</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31726</t>
+          <t>29254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80795</t>
+          <t>79834</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77348</t>
+          <t>76120</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109692</t>
+          <t>107546</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115524</t>
+          <t>117201</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>177214</t>
+          <t>177099</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2099075</t>
+          <t>2098423</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2880630</t>
+          <t>2878909</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2834750</t>
+          <t>2815800</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3128183</t>
+          <t>3115505</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4975269</t>
+          <t>4926368</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5953493</t>
+          <t>5946524</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26695</t>
+          <t>27767</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>59270</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24058</t>
+          <t>24786</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45519</t>
+          <t>47802</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56230</t>
+          <t>55599</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>94041</t>
+          <t>98314</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>444820</t>
+          <t>446533</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1238411</t>
+          <t>1238210</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>413883</t>
+          <t>420100</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>705484</t>
+          <t>722606</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>904754</t>
+          <t>910950</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1903282</t>
+          <t>1957407</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C04_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Clase-trans_orig.xlsx
@@ -725,17 +725,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>424562</t>
+          <t>462918</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>405588</t>
+          <t>442680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>439357</t>
+          <t>478862</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>371860</t>
+          <t>404394</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>357479</t>
+          <t>388544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>383340</t>
+          <t>417161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>796422</t>
+          <t>867312</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>771655</t>
+          <t>842710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>889744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -838,67 +838,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17069</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6673</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3420</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11368</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6288</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3051</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12279</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>25742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71273</t>
+          <t>78001</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56947</t>
+          <t>61942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88326</t>
+          <t>95900</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66316</t>
+          <t>74237</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55163</t>
+          <t>61396</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79434</t>
+          <t>88442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>137589</t>
+          <t>152238</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119780</t>
+          <t>131614</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161569</t>
+          <t>175147</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>502795</t>
+          <t>548253</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>502795</t>
+          <t>548253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>502795</t>
+          <t>548253</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>444465</t>
+          <t>485305</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>444465</t>
+          <t>485305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>444465</t>
+          <t>485305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>947260</t>
+          <t>1033558</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>947260</t>
+          <t>1033558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>947260</t>
+          <t>1033558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>386915</t>
+          <t>411941</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370326</t>
+          <t>396549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400275</t>
+          <t>425382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>317616</t>
+          <t>349321</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>305926</t>
+          <t>335967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329010</t>
+          <t>361560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>704531</t>
+          <t>761260</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>684593</t>
+          <t>738957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721639</t>
+          <t>778932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>61511</t>
+          <t>67195</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47702</t>
+          <t>54161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78117</t>
+          <t>82460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60438</t>
+          <t>69042</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49051</t>
+          <t>57184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71647</t>
+          <t>82464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>121949</t>
+          <t>136237</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105410</t>
+          <t>119279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141473</t>
+          <t>158156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>451246</t>
+          <t>482165</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451246</t>
+          <t>482165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451246</t>
+          <t>482165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>833826</t>
+          <t>905307</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>833826</t>
+          <t>905307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833826</t>
+          <t>905307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,67 +1637,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>363797</t>
+          <t>398692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151959</t>
+          <t>377613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>581549</t>
+          <t>412523</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>87,9%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>163116</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>155875</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>169417</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>87,32%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>145157</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>138303</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>151034</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>508954</t>
+          <t>561809</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>195890</t>
+          <t>543046</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>728296</t>
+          <t>579079</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>297497</t>
+          <t>65635</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77591</t>
+          <t>51412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>511679</t>
+          <t>83879</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14377</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>29717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>317376</t>
+          <t>87939</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96383</t>
+          <t>71046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>636965</t>
+          <t>106045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>665977</t>
+          <t>469336</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>665977</t>
+          <t>469336</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>665977</t>
+          <t>469336</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166254</t>
+          <t>186799</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166254</t>
+          <t>186799</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166254</t>
+          <t>186799</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>832231</t>
+          <t>656135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>832231</t>
+          <t>656135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>832231</t>
+          <t>656135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>879564</t>
+          <t>967458</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>844663</t>
+          <t>942114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>904589</t>
+          <t>991337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>877438</t>
+          <t>744197</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>844306</t>
+          <t>725375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>927210</t>
+          <t>760605</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1757002</t>
+          <t>1711654</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1711303</t>
+          <t>1679037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1828483</t>
+          <t>1740137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20338</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>17472</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>32284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>142030</t>
+          <t>148330</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118328</t>
+          <t>124442</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177768</t>
+          <t>174173</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>94103</t>
+          <t>108052</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46329</t>
+          <t>92301</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>125056</t>
+          <t>125836</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>256382</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>169227</t>
+          <t>229778</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>280074</t>
+          <t>288011</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1033799</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033799</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1033799</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>976808</t>
+          <t>859172</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>976808</t>
+          <t>859172</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>976808</t>
+          <t>859172</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2010607</t>
+          <t>1989929</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2010607</t>
+          <t>1989929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2010607</t>
+          <t>1989929</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>416660</t>
+          <t>500705</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>400159</t>
+          <t>482777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>431383</t>
+          <t>515224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>664476</t>
+          <t>712053</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>494173</t>
+          <t>695730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>731263</t>
+          <t>728023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1081137</t>
+          <t>1212758</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>894738</t>
+          <t>1189843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1149629</t>
+          <t>1236071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>17262</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>31296</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>47948</t>
+          <t>52848</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34895</t>
+          <t>39073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63041</t>
+          <t>68273</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>166970</t>
+          <t>107302</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99318</t>
+          <t>92153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>339751</t>
+          <t>124117</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>214918</t>
+          <t>160150</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>146464</t>
+          <t>137391</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>405137</t>
+          <t>181888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>474352</t>
+          <t>565676</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>474352</t>
+          <t>565676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>474352</t>
+          <t>565676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>838963</t>
+          <t>828156</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>838963</t>
+          <t>828156</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>838963</t>
+          <t>828156</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1313316</t>
+          <t>1393832</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313316</t>
+          <t>1393832</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1313316</t>
+          <t>1393832</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>185576</t>
+          <t>186892</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>158122</t>
+          <t>162443</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>208805</t>
+          <t>207152</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>659886</t>
+          <t>732765</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>641247</t>
+          <t>712317</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>675070</t>
+          <t>749004</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>845462</t>
+          <t>919657</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>807836</t>
+          <t>884284</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>871519</t>
+          <t>945621</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20685</t>
+          <t>16731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27127</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>51060</t>
+          <t>46921</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29254</t>
+          <t>27667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>79834</t>
+          <t>71307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,22 +3266,22 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>90538</t>
+          <t>100205</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76120</t>
+          <t>84413</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107546</t>
+          <t>119033</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>141597</t>
+          <t>147126</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>117201</t>
+          <t>122673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>177099</t>
+          <t>180441</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>758706</t>
+          <t>841416</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>758706</t>
+          <t>841416</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>758706</t>
+          <t>841416</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>999213</t>
+          <t>1078644</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>999213</t>
+          <t>1078644</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>999213</t>
+          <t>1078644</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2657074</t>
+          <t>2928604</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2098423</t>
+          <t>2876473</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2878909</t>
+          <t>2972987</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3036432</t>
+          <t>3105846</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2815800</t>
+          <t>3068300</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3115505</t>
+          <t>3142432</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5693506</t>
+          <t>6034450</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4926368</t>
+          <t>5976052</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5946524</t>
+          <t>6090083</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>40284</t>
+          <t>45880</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27767</t>
+          <t>32193</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59270</t>
+          <t>64348</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,67 +3609,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>37003</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47802</t>
+          <t>50222</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>82883</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>65297</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>103508</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>73385</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>55599</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>98314</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>671318</t>
+          <t>458930</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>446533</t>
+          <t>415547</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1238210</t>
+          <t>509258</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>498244</t>
+          <t>481142</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>420100</t>
+          <t>446392</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>722606</t>
+          <t>517595</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1169561</t>
+          <t>940072</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>910950</t>
+          <t>888661</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1957407</t>
+          <t>999320</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3368676</t>
+          <t>3433414</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3368676</t>
+          <t>3433414</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3368676</t>
+          <t>3433414</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3567776</t>
+          <t>3623991</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3567776</t>
+          <t>3623991</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3567776</t>
+          <t>3623991</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6936452</t>
+          <t>7057405</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6936452</t>
+          <t>7057405</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6936452</t>
+          <t>7057405</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
